--- a/backtest_runs/20260410_193731/by_symbol/TCORP/TCORP.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/TCORP/TCORP.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>-793.9600000000015</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>111909.4</v>
@@ -771,7 +771,7 @@
         <v>-4418.560000000004</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>111495.16</v>
@@ -817,7 +817,7 @@
         <v>-724.9199999999906</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>110770.24</v>
@@ -1139,7 +1139,7 @@
         <v>-1104.640000000001</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>116776.72</v>
@@ -1185,7 +1185,7 @@
         <v>-1622.439999999996</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>115154.28</v>
@@ -1231,7 +1231,7 @@
         <v>-1898.600000000002</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>113255.68</v>
@@ -1323,7 +1323,7 @@
         <v>-7767</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>105695.8</v>
@@ -1415,7 +1415,7 @@
         <v>-2243.800000000007</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>105316.08</v>
@@ -1553,7 +1553,7 @@
         <v>-345.2000000000049</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>107283.72</v>
@@ -1645,7 +1645,7 @@
         <v>-3072.280000000002</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>105247.04</v>
